--- a/output/第10期計画_将来推計_第3段階_給付費と保険料.xlsx
+++ b/output/第10期計画_将来推計_第3段階_給付費と保険料.xlsx
@@ -1174,7 +1174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1391,12 +1391,292 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>【2　この対比から言えること】</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="140" customHeight="1">
+          <t>【2　期別の保険料基準額（見える化システムの出力）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第6節に掲げていた期別の対照表を本シートへ移した（令和8年9月29日のご指示による）。計画素案の本文には、第9期は実績が計画を下回り乖離が標準給付費見込額に集中していること、実績から算定した平均6,208円が別の経路の値と0.2％の差で一致することのみを残している。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>第7期 取崩前</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>第7期 取崩後</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>第8期 取崩前／取崩後</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>第9期 取崩前</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>第9期 取崩後</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>計画値　合計</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>6,233</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>6,077</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>6,330／6,237</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>6,553</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>6,428</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち標準給付費見込額</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>5,925</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>5,777</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>5,903／5,817</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>6,125</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>6,008</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち地域支援事業費</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="inlineStr">
+        <is>
+          <t>427／421</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>428</t>
+        </is>
+      </c>
+      <c r="F17" s="19" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>実績値　合計</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>6,100</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>6,021</t>
+        </is>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>6,334／6,334</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="inlineStr">
+        <is>
+          <t>6,196</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="inlineStr">
+        <is>
+          <t>6,069</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち標準給付費見込額</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>5,721</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>5,647</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>5,927／5,927</t>
+        </is>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>5,763</t>
+        </is>
+      </c>
+      <c r="F19" s="19" t="inlineStr">
+        <is>
+          <t>5,645</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　うち地域支援事業費</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>407／407</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="F20" s="19" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>対計画比　合計</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>98％</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>99％</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>100％／102％</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>95％</t>
+        </is>
+      </c>
+      <c r="F21" s="19" t="inlineStr">
+        <is>
+          <t>94％</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="92" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>単位：円（月額）。出所は地域包括ケア「見える化」システム。
+注1）見える化システムの計画値は算定上の月額である。条例で採用した基準額（第7期6,077円・第8期6,300円・第9期6,400円）とは、百円未満の端数処理により一致しない場合がある。第9期の実績は令和8年度分が未登録の状態での値である。
+注2）第8期は実績が計画を上回った（取崩後102％）が、第9期は逆に下回っている（取崩後94％）。乖離は標準給付費見込額に集中しており（92％）、地域支援事業費はほぼ計画どおりである（99％）。
+注3）見える化システムの第9期実績（準備基金取崩前）6,196円は、年報から算定した令和6年度6,063円・令和7年度6,352円の平均6,208円と12円（0.2％）の差で一致する。また計画値の取崩前6,553円と取崩後6,428円の差125円は、第9期計画の基金取崩額40,000,000円に対応する。2つの経路で算定した値が一致するため、第10期の算定の出発点として用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>【3　この対比から言えること】</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="140" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>見える化システムの自然体推計6,238円は、内訳が出力されないため、項目ごとに突き合わせることができません。ただし、給付費を第9期の実績年率で置いた場合の本表の値は6144円で、6,238円との差は9円（0.1％）にとどまります。他の前提（収納率・基金取崩額・第1号負担割合）は同じであるため、見える化の保険料の推計は給付費を第9期の実績の水準で置いており、同じ見える化システムが出力する自然体給付費推計の伸びを織り込んでいない可能性があります。これは受託者の推定であり、確認したものではありません。
 第10期の計画に用いる値は、見える化の出力をそのまま採るのではなく、本表のように内訳を組み立てたうえで決めることが必要です。内訳を示せなければ、住民及び委員に対して保険料の水準を説明することができないためです。
@@ -1405,12 +1685,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
